--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Equipo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Equipos auxiliares" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fichas (formulario)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cómo usar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipos auxiliares" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fichas (formulario)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Equipo'!$A$2:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Equipo'!$A$2:$P$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -845,15 +845,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Frank Morales</t>
+          <t>Laura Fernández</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>asesores</t>
@@ -861,7 +863,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Asesor</t>
+          <t>Asesora</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -876,35 +878,55 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>62</v>
+      </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>26-oct</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>+18296973316</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Laura Fernández</t>
+          <t>Tomás Lorenzo</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -913,7 +935,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Asesora</t>
+          <t>Asesor</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -937,20 +959,20 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>26-oct</t>
+          <t>14-mar</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>+18296973316</t>
+          <t>+80986364340</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -967,30 +989,30 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Tomás Lorenzo</t>
+          <t>Camila Fernández Hazim</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>asesores</t>
+        <v>26</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Asesor</t>
+          <t>Coord. Guía</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1005,29 +1027,31 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="J7" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="n">
+        <v>2017</v>
+      </c>
       <c r="L7" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>14-mar</t>
+          <t>18-ago</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>+80986364340</t>
+          <t>+18099615497</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -1039,7 +1063,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Camila Fernández Hazim</t>
+          <t>Priscilla Hidalgo Pou</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1048,7 +1072,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1081,22 +1105,22 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>18-ago</t>
+          <t>16-jul</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>+18099615497</t>
+          <t>+18294783840</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -1113,7 +1137,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Priscilla Hidalgo Pou</t>
+          <t>Darianny Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1122,7 +1146,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1131,19 +1155,19 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Coord. Guía</t>
+          <t>Guía</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Betania</t>
@@ -1151,26 +1175,24 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>2011</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>16-jul</t>
+          <t>30-ene</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>+18294783840</t>
+          <t>+8293726925</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1187,16 +1209,16 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Darianny Rodriguez Belliard</t>
+          <t>Fernando Cordero</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -1229,25 +1251,27 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>2022</v>
+      </c>
       <c r="L10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>30-ene</t>
+          <t>20-dic</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>+8293726925</t>
+          <t>+18096398714</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -1259,7 +1283,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fernando Cordero</t>
+          <t>Franklin De Jesús Silverio Delgadillo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1268,7 +1292,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1301,27 +1325,27 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>20-dic</t>
+          <t>18-feb</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>+18096398714</t>
+          <t>+84986485100</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1333,16 +1357,16 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Franklin De Jesús Silverio Delgadillo</t>
+          <t>Ivanna Marien Mercedes Sosa</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -1371,7 +1395,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
@@ -1381,21 +1405,21 @@
         <v>2018</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>18-feb</t>
+          <t>9-nov</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>+84986485100</t>
+          <t>+82999467310</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1407,7 +1431,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Ivanna Marien Mercedes Sosa</t>
+          <t>Jhonnalia Franchesca Silvestre Guzmán</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1416,7 +1440,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1445,31 +1469,31 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>9-nov</t>
+          <t>20-oct</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>+82999467310</t>
+          <t>+82991806660</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1481,16 +1505,16 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Jhonnalia Franchesca Silvestre Guzmán</t>
+          <t>Jonathan Andres Medina Mota</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -1523,22 +1547,22 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>20-oct</t>
+          <t>26-sep</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>+82991806660</t>
+          <t>+8097792446</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1555,7 +1579,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Jonathan Andres Medina Mota</t>
+          <t>Juan Pablo Argüello Alzate</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1564,7 +1588,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1593,26 +1617,26 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>26-sep</t>
+          <t>21-ene</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>+8097792446</t>
+          <t>+18298790121</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1629,16 +1653,16 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Juan Pablo Argüello Alzate</t>
+          <t>Luisa Maria Fiorentino Brugal</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -1667,26 +1691,26 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>21-ene</t>
+          <t>19-may</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>+18298790121</t>
+          <t>+18099722327</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1703,16 +1727,16 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Luisa Maria Fiorentino Brugal</t>
+          <t>Oliver Rafael De León Ramírez</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1745,27 +1769,27 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>19-may</t>
+          <t>24-abr</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>+18099722327</t>
+          <t>+80926368020</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -1777,16 +1801,16 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Oliver Rafael De León Ramírez</t>
+          <t>Victoria Lorenzo Rivera</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -1819,27 +1843,27 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>24-abr</t>
+          <t>21-sep</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>+80926368020</t>
+          <t>+80988265230</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -1851,7 +1875,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Victoria Lorenzo Rivera</t>
+          <t>Wilka María Reyes Mota</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1860,7 +1884,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -1893,27 +1917,27 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>21-sep</t>
+          <t>8-sep</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>+80988265230</t>
+          <t>+18298618355</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1925,7 +1949,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Wilka María Reyes Mota</t>
+          <t>Yelaxni Mota</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1934,7 +1958,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -1963,26 +1987,24 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v>2023</v>
-      </c>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>8-sep</t>
+          <t>25-sep</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>+18298618355</t>
+          <t>+18094911672</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1999,30 +2021,30 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Yelaxni Mota</t>
+          <t>Johnnito Richiez Brugal</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>guias</t>
+        <v>41</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Guía</t>
+          <t>Coord. Cocina</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2037,29 +2059,31 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>2005</v>
+      </c>
       <c r="L21" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>25-sep</t>
+          <t>23-oct</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>+18094911672</t>
+          <t>+82926441760</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -2071,69 +2095,67 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Johnnito Richiez Brugal</t>
+          <t>Paloma Mendez</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Coord. Cocina</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>27-jun</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>+80986076300</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
           <t>M</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Coord. Cocina</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>2005</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>23-oct</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>+82926441760</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>XL</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -2145,16 +2167,16 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Paloma Mendez</t>
+          <t>Adrián Francisco Santana Puente</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
@@ -2163,22 +2185,22 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Coord. Cocina</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2187,20 +2209,22 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>2025</v>
+      </c>
       <c r="L23" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>27-jun</t>
+          <t>22-ene</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>+80986076300</t>
+          <t>+18296405377</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2217,16 +2241,16 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Adrián Francisco Santana Puente</t>
+          <t>Ambar Liz Jáquez Lebrón</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -2269,17 +2293,17 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>22-ene</t>
+          <t>22-sep</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>+18296405377</t>
+          <t>+18492441217</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -2291,7 +2315,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Ambar Liz Jáquez Lebrón</t>
+          <t>Brianelis Abreu Calderón</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2300,7 +2324,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
@@ -2343,12 +2367,12 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>22-sep</t>
+          <t>12-nov</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>+18492441217</t>
+          <t>+18098421217</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2365,7 +2389,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Brianelis Abreu Calderón</t>
+          <t>Candy Elizabeth Gatwood Ramos</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2374,7 +2398,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -2398,36 +2422,36 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>12-nov</t>
+          <t>5-ene</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>+18098421217</t>
+          <t>+8495384498</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -2439,7 +2463,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Candy Elizabeth Gatwood Ramos</t>
+          <t>Chantal Melissa Carpio Jiménez</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2448,7 +2472,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
@@ -2472,36 +2496,36 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Higüey / SPM</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>5-ene</t>
+          <t>24-dic</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>+8495384498</t>
+          <t>+18292608939</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -2513,7 +2537,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Chantal Melissa Carpio Jiménez</t>
+          <t>Dayrelins Jazmin Santana Salas</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2522,7 +2546,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
@@ -2546,36 +2570,36 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Higüey / SPM</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>24-dic</t>
+          <t>30-ago</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>+18292608939</t>
+          <t>+8094264150</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2587,7 +2611,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Dayrelins Jazmin Santana Salas</t>
+          <t>Fabelle maciel fabian bello</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2596,7 +2620,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
@@ -2629,27 +2653,27 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>30-ago</t>
+          <t>11-ago</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>+8094264150</t>
+          <t>+18292859257</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -2661,16 +2685,16 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Fabelle maciel fabian bello</t>
+          <t>Guido Mardonado</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
@@ -2703,27 +2727,25 @@
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>2018</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>11-ago</t>
+          <t>30-nov</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>+18292859257</t>
+          <t>+15512144384</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -2735,67 +2757,69 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Guido Mardonado</t>
+          <t>Jordelis Mateo</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>26-jul</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>+82961012540</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
           <t>M</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>30-nov</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>+15512144384</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -2807,16 +2831,16 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Jordelis Mateo</t>
+          <t>Kelvin Alexis Ventura Santana</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
@@ -2845,26 +2869,26 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>26-jul</t>
+          <t>28-jul</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>+82961012540</t>
+          <t>+18094633990</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -2881,16 +2905,16 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Kelvin Alexis Ventura Santana</t>
+          <t>Maria del Carmen Mejías Mateo</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
@@ -2923,22 +2947,22 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>28-jul</t>
+          <t>29-ago</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>+18094633990</t>
+          <t>+8297137943</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -2955,7 +2979,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Maria del Carmen Mejías Mateo</t>
+          <t>Olanlly</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2963,9 +2987,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
-        <v>42</v>
-      </c>
+      <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -2988,48 +3010,26 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>2016</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>29-ago</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>+8297137943</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr"/>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Olanlly</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Risaira Santana Rosario</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3087,7 +3087,9 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3110,26 +3112,48 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr"/>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>29-jun</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>+18292032829</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Risaira Santana Rosario</t>
+          <t>Risairi Santana Rosario</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3138,7 +3162,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
@@ -3162,7 +3186,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -3171,27 +3195,27 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>29-jun</t>
+          <t>28-mar</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>+18292032829</t>
+          <t>+18293762582</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3203,16 +3227,16 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Risairi Santana Rosario</t>
+          <t>Roberto Figueroa</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
@@ -3236,7 +3260,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3245,27 +3269,25 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>2025</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>28-mar</t>
+          <t>12-may</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>+18293762582</t>
+          <t>+18097171329</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3277,17 +3299,15 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Roberto Figueroa</t>
+          <t>Roselyn</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>45</v>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3310,54 +3330,36 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>55</v>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>12-may</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>+18097171329</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Roselyn</t>
+          <t>Tommy Nova Nolasco</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3380,88 +3382,108 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="inlineStr"/>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>7-sep</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>+18492666296</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Tommy Nova Nolasco</t>
+          <t>Wirna Miguelina Stapleton Pilier</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>29-sep</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>+82980199270</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
           <t>M</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Belén</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>7-sep</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>+18492666296</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>XL</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3473,30 +3495,30 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Wirna Miguelina Stapleton Pilier</t>
+          <t>José Ángel Tusen Russo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
+        <v>26</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>musica</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Cocina</t>
+          <t>Coord. Música</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -3511,29 +3533,31 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>2017</v>
+      </c>
       <c r="L42" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>29-sep</t>
+          <t>30-oct</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>+82980199270</t>
+          <t>+8493521430</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -3545,17 +3569,15 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>José Ángel Tusen Russo</t>
+          <t>Daylin</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>26</v>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
       <c r="D43" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3563,63 +3585,41 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Coord. Música</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>2017</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>30-oct</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>+8493521430</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Daylin</t>
+          <t>Dorian Elina Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3627,7 +3627,9 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3650,26 +3652,48 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
-      <c r="O44" s="4" t="inlineStr"/>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>21-mar</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>+82998609950</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Dorian Elina Rodriguez Belliard</t>
+          <t>Ismarie Sthepanie Constanzo Ramos</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3678,7 +3702,7 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -3707,26 +3731,26 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>El Seibo / SPM</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>21-mar</t>
+          <t>14-jun</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>+82998609950</t>
+          <t>+18493865474</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3743,16 +3767,16 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Ismarie Sthepanie Constanzo Ramos</t>
+          <t>Leober Carrion Soriank</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
@@ -3781,26 +3805,26 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>El Seibo / SPM</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>14-jun</t>
+          <t>4-oct</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>+18493865474</t>
+          <t>+18294401305</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3817,16 +3841,16 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Leober Carrion Soriank</t>
+          <t>Mary Carmen Ramírez Vásquez</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
@@ -3859,22 +3883,22 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>4-oct</t>
+          <t>29-ago</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>+18294401305</t>
+          <t>+18296937582</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -3891,25 +3915,23 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Mary Carmen Ramírez Vásquez</t>
+          <t>Frank Morales</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>musica</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>asesores</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Asesor + Banderín</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3924,48 +3946,26 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>29-ago</t>
-        </is>
-      </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>+18296937582</t>
-        </is>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Johany</t>
+          <t>Johanny García</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -4015,7 +4015,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Petra</t>
+          <t>Mary "Peta" Morales</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -4065,7 +4065,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Padre Paul Ramírez</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Sor Angelina</t>
+          <t>Sor Angelina Lebrón</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Rep. Diocesano LV #1</t>
+          <t>Asesor SPM (por definir)</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Asesor La Vega</t>
+          <t>Asesor Comunidad SPM</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4215,12 +4215,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Rep. Diocesano SD #1</t>
+          <t>Leticia González</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Asesor SD</t>
+          <t>Asesora Comunidad La Vega</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Rep. Diocesano SD #2</t>
+          <t>Marleny</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr"/>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Asesor SD</t>
+          <t>Asesora Comunidad SD</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Rep. Diocesano LV #2</t>
+          <t>Rep. Punta Cana (pendiente)</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Asesor La Vega (opcional)</t>
+          <t>Asesor Comunidad PC</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -4362,28 +4362,78 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Sandrita</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr"/>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Asesora Comunidad SD</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
+      <c r="N57" s="11" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P56"/>
+  <autoFilter ref="A2:P57"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="B3:B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B3:B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"F,M,?"</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D3:D57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"directores,asesores,guias,cocina,musica,asesores_cocina,asesores_espirituales,asesores_diocesanos"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F3:F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G3:G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Belén,Betania,Por confirmar"</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="P3:P57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6553,7 +6603,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Versión de datos: v4-2026-06-02 · 46 operativos + 8 ampliados = 54 en el retiro.</t>
+          <t>Versión de datos: v5-2026-06-02 · 46 operativos + 9 ampliados = 55 en el retiro.</t>
         </is>
       </c>
     </row>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usar" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Equipo'!$A$2:$P$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Equipo'!$A$2:$P$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -110,17 +110,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="004A372A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="006E7F4C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3E4BE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004A372A"/>
       </patternFill>
     </fill>
     <fill>
@@ -184,16 +184,16 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,7 +202,7 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3299,15 +3299,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Roselyn</t>
+          <t>Tommy Nova Nolasco</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3330,88 +3332,108 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
+          <t>Belén</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>7-sep</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>+18492666296</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Tommy Nova Nolasco</t>
+          <t>Wirna Miguelina Stapleton Pilier</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>29-sep</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>+82980199270</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
           <t>M</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Belén</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>7-sep</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>+18492666296</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>XL</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3423,30 +3445,30 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Wirna Miguelina Stapleton Pilier</t>
+          <t>José Ángel Tusen Russo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
+        <v>26</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>musica</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Cocina</t>
+          <t>Coord. Música</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -3461,29 +3483,31 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>2017</v>
+      </c>
       <c r="L41" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>29-sep</t>
+          <t>30-oct</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>+82980199270</t>
+          <t>+8493521430</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3495,17 +3519,15 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>José Ángel Tusen Russo</t>
+          <t>Daylin</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>26</v>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3513,12 +3535,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Coord. Música</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -3528,48 +3550,26 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>2017</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>30-oct</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>+8493521430</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Daylin</t>
+          <t>Dorian Elina Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3577,7 +3577,9 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3600,26 +3602,48 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr"/>
-      <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="inlineStr"/>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>21-mar</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>+82998609950</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Dorian Elina Rodriguez Belliard</t>
+          <t>Ismarie Sthepanie Constanzo Ramos</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3628,7 +3652,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
@@ -3657,26 +3681,26 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>El Seibo / SPM</t>
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>21-mar</t>
+          <t>14-jun</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>+82998609950</t>
+          <t>+18493865474</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3693,16 +3717,16 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Ismarie Sthepanie Constanzo Ramos</t>
+          <t>Leober Carrion Soriano</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -3731,26 +3755,26 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>El Seibo / SPM</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>14-jun</t>
+          <t>4-oct</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>+18493865474</t>
+          <t>+18294401305</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3767,16 +3791,16 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Leober Carrion Soriank</t>
+          <t>Mary Carmen Ramírez Vásquez</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
@@ -3809,22 +3833,22 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>4-oct</t>
+          <t>29-ago</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>+18294401305</t>
+          <t>+18296937582</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3841,25 +3865,23 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Mary Carmen Ramírez Vásquez</t>
+          <t>Frank Morales</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>musica</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>asesores</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Asesor + Banderín</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3874,48 +3896,26 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>29-ago</t>
-        </is>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>+18296937582</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Frank Morales</t>
+          <t>Padre Paul Ramírez</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3924,14 +3924,14 @@
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>asesores</t>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>asesores_espirituales</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Asesor + Banderín</t>
+          <t>Asesor Espiritual transversal</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3963,477 +3963,527 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sor Angelina Lebrón</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>asesores_espirituales</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Asesora Espiritual transversal</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Johanny García</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr"/>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr"/>
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>asesores_cocina</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>Asesora Cocina</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr"/>
-      <c r="K49" s="11" t="inlineStr"/>
-      <c r="L49" s="11" t="inlineStr"/>
-      <c r="M49" s="11" t="inlineStr"/>
-      <c r="N49" s="11" t="inlineStr"/>
-      <c r="O49" s="11" t="inlineStr"/>
-      <c r="P49" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="12" t="inlineStr"/>
+      <c r="K50" s="12" t="inlineStr"/>
+      <c r="L50" s="12" t="inlineStr"/>
+      <c r="M50" s="12" t="inlineStr"/>
+      <c r="N50" s="12" t="inlineStr"/>
+      <c r="O50" s="12" t="inlineStr"/>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Mary "Peta" Morales</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr"/>
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>asesores_cocina</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Asesora Cocina</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr"/>
-      <c r="J50" s="11" t="inlineStr"/>
-      <c r="K50" s="11" t="inlineStr"/>
-      <c r="L50" s="11" t="inlineStr"/>
-      <c r="M50" s="11" t="inlineStr"/>
-      <c r="N50" s="11" t="inlineStr"/>
-      <c r="O50" s="11" t="inlineStr"/>
-      <c r="P50" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Padre Paul Ramírez</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="12" t="inlineStr"/>
+      <c r="K51" s="12" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="12" t="inlineStr"/>
+      <c r="N51" s="12" t="inlineStr"/>
+      <c r="O51" s="12" t="inlineStr"/>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Kamila Todd</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Backup Guía</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="12" t="inlineStr"/>
+      <c r="K52" s="12" t="inlineStr"/>
+      <c r="L52" s="12" t="inlineStr"/>
+      <c r="M52" s="12" t="inlineStr"/>
+      <c r="N52" s="12" t="inlineStr"/>
+      <c r="O52" s="12" t="inlineStr"/>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Leticia González</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr"/>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Asesora Comunidad La Vega</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="12" t="inlineStr"/>
+      <c r="K53" s="12" t="inlineStr"/>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
+      <c r="N53" s="12" t="inlineStr"/>
+      <c r="O53" s="12" t="inlineStr"/>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>Marleny</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr"/>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Asesora Comunidad SD</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="12" t="inlineStr"/>
+      <c r="K54" s="12" t="inlineStr"/>
+      <c r="L54" s="12" t="inlineStr"/>
+      <c r="M54" s="12" t="inlineStr"/>
+      <c r="N54" s="12" t="inlineStr"/>
+      <c r="O54" s="12" t="inlineStr"/>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>Rodolfo Telémaco</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>asesores_espirituales</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>Asesor Espiritual</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Backup Guía</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr"/>
-      <c r="K51" s="11" t="inlineStr"/>
-      <c r="L51" s="11" t="inlineStr"/>
-      <c r="M51" s="11" t="inlineStr"/>
-      <c r="N51" s="11" t="inlineStr"/>
-      <c r="O51" s="11" t="inlineStr"/>
-      <c r="P51" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>Sor Angelina Lebrón</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="12" t="inlineStr"/>
+      <c r="K55" s="12" t="inlineStr"/>
+      <c r="L55" s="12" t="inlineStr"/>
+      <c r="M55" s="12" t="inlineStr"/>
+      <c r="N55" s="12" t="inlineStr"/>
+      <c r="O55" s="12" t="inlineStr"/>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Sandrita</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>asesores_espirituales</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Asesora Espiritual</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr"/>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Asesora Comunidad SD</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr"/>
-      <c r="K52" s="11" t="inlineStr"/>
-      <c r="L52" s="11" t="inlineStr"/>
-      <c r="M52" s="11" t="inlineStr"/>
-      <c r="N52" s="11" t="inlineStr"/>
-      <c r="O52" s="11" t="inlineStr"/>
-      <c r="P52" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Asesor SPM (por definir)</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="12" t="inlineStr"/>
+      <c r="K56" s="12" t="inlineStr"/>
+      <c r="L56" s="12" t="inlineStr"/>
+      <c r="M56" s="12" t="inlineStr"/>
+      <c r="N56" s="12" t="inlineStr"/>
+      <c r="O56" s="12" t="inlineStr"/>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Scarlett Nivar</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Backup Guía</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr"/>
+      <c r="J57" s="12" t="inlineStr"/>
+      <c r="K57" s="12" t="inlineStr"/>
+      <c r="L57" s="12" t="inlineStr"/>
+      <c r="M57" s="12" t="inlineStr"/>
+      <c r="N57" s="12" t="inlineStr"/>
+      <c r="O57" s="12" t="inlineStr"/>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Vacante Cocina (varón — candidato Randolph)</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr"/>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>Asesor Comunidad SPM</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr"/>
-      <c r="K53" s="11" t="inlineStr"/>
-      <c r="L53" s="11" t="inlineStr"/>
-      <c r="M53" s="11" t="inlineStr"/>
-      <c r="N53" s="11" t="inlineStr"/>
-      <c r="O53" s="11" t="inlineStr"/>
-      <c r="P53" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Leticia González</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr"/>
-      <c r="D54" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>Asesora Comunidad La Vega</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr"/>
-      <c r="K54" s="11" t="inlineStr"/>
-      <c r="L54" s="11" t="inlineStr"/>
-      <c r="M54" s="11" t="inlineStr"/>
-      <c r="N54" s="11" t="inlineStr"/>
-      <c r="O54" s="11" t="inlineStr"/>
-      <c r="P54" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Marleny</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr"/>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Asesora Comunidad SD</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr"/>
-      <c r="K55" s="11" t="inlineStr"/>
-      <c r="L55" s="11" t="inlineStr"/>
-      <c r="M55" s="11" t="inlineStr"/>
-      <c r="N55" s="11" t="inlineStr"/>
-      <c r="O55" s="11" t="inlineStr"/>
-      <c r="P55" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Rep. Punta Cana (pendiente)</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr"/>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Asesor Comunidad PC</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr"/>
-      <c r="K56" s="11" t="inlineStr"/>
-      <c r="L56" s="11" t="inlineStr"/>
-      <c r="M56" s="11" t="inlineStr"/>
-      <c r="N56" s="11" t="inlineStr"/>
-      <c r="O56" s="11" t="inlineStr"/>
-      <c r="P56" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Sandrita</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr"/>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>Asesora Comunidad SD</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr"/>
-      <c r="K57" s="11" t="inlineStr"/>
-      <c r="L57" s="11" t="inlineStr"/>
-      <c r="M57" s="11" t="inlineStr"/>
-      <c r="N57" s="11" t="inlineStr"/>
-      <c r="O57" s="11" t="inlineStr"/>
-      <c r="P57" s="11" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="12" t="inlineStr"/>
+      <c r="K58" s="12" t="inlineStr"/>
+      <c r="L58" s="12" t="inlineStr"/>
+      <c r="M58" s="12" t="inlineStr"/>
+      <c r="N58" s="12" t="inlineStr"/>
+      <c r="O58" s="12" t="inlineStr"/>
+      <c r="P58" s="12" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P57"/>
+  <autoFilter ref="A2:P58"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="B3:B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B3:B58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"F,M,?"</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D3:D58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"directores,asesores,guias,cocina,musica,asesores_cocina,asesores_espirituales,asesores_diocesanos"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F3:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G3:G58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Belén,Betania,Por confirmar"</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="P3:P58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4447,7 +4497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4488,12 +4538,12 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Donaciones</t>
+          <t>Recaudación y Donaciones</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Levantamiento de fondos y aportes en especie. Puede incluir gente fuera del equipo operativo.</t>
+          <t>Levantamiento de fondos + aportes en especie. Un solo equipo. Puede incluir gente fuera del equipo operativo.</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -4506,12 +4556,12 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Guagua</t>
+          <t>Guagua (Transporte)</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>Coordinación de transporte para todos los traslados (formaciones, retiro, avanzada).</t>
+          <t>Coordinación de transporte para formaciones, retiro, avanzada. Equipo externo (no pernocta en la casa).</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -4538,6 +4588,24 @@
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr"/>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Intersección (espiritual)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Equipo espiritual transversal del retiro: oración, intercesión, acompañamiento. Liderado por los Asesores Espirituales (Paul + Sor Angelina) más etecianos de oración.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Asesores Espirituales</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6420,7 +6488,7 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>Leober Carrion Soriank</t>
+          <t>Leober Carrion Soriano</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -6603,7 +6671,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Versión de datos: v5-2026-06-02 · 46 operativos + 9 ampliados = 55 en el retiro.</t>
+          <t>Versión de datos: v7-2026-06-02 · 47 operativos + 9 ampliados = 56 en el retiro.</t>
         </is>
       </c>
     </row>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -4543,12 +4543,12 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Levantamiento de fondos + aportes en especie. Un solo equipo. Puede incluir gente fuera del equipo operativo.</t>
+          <t>Levantamiento de fondos + aportes en especie. Donaciones a empresas/particulares = responsabilidad de Directores (delegable).</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Coords cocina + Roberto</t>
+          <t>Co-Dir + Coords de cocina + Roberto</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>Coordinación de transporte para formaciones, retiro, avanzada. Equipo externo (no pernocta en la casa).</t>
+          <t>Coordinación de transporte para formaciones, retiro y avanzada. Equipo externo (no pernocta en la casa).</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Diseño y ejecución de la actividad principal del Profondo (31-jul al 2-ago). Puede integrar gente fuera del equipo.</t>
+          <t>Profondo #1 = rifa (primera actividad). Profondo #2 = venta de comida / garaje.</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Equipo espiritual transversal del retiro: oración, intercesión, acompañamiento. Liderado por los Asesores Espirituales (Paul + Sor Angelina) más etecianos de oración.</t>
+          <t>Equipo espiritual transversal: oración, intercesión, acompañamiento.</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Asesores Espirituales</t>
+          <t>Asesores Espirituales (Padre Paul + Sor Angelina)</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr"/>
@@ -6671,7 +6671,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Versión de datos: v7-2026-06-02 · 47 operativos + 9 ampliados = 56 en el retiro.</t>
+          <t>Versión de datos: v8-2026-06-02 · 47 operativos + 9 ampliados = 56 en el retiro.</t>
         </is>
       </c>
     </row>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -2611,7 +2611,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Fabelle maciel fabian bello</t>
+          <t>Fabelly Maciel Fabian Bello</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2685,7 +2685,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Guido Mardonado</t>
+          <t>Guido Maldonado</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -5888,7 +5888,7 @@
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>Fabelle maciel fabian bello</t>
+          <t>Fabelly Maciel Fabian Bello</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -5936,7 +5936,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>Guido Mardonado</t>
+          <t>Guido Maldonado</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -4065,7 +4065,7 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Mary "Peta" Morales</t>
+          <t>Mary "Petra" Morales</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>Guido Mardonado, Padre, 809-844-7093</t>
+          <t>Guido Maldonado, Padre, 809-844-7093</t>
         </is>
       </c>
     </row>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Co-Dir + Coords de cocina + Roberto</t>
+          <t>Por nombrar (Co-Dir decide)</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr"/>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -3079,17 +3079,15 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Risaira Santana Rosario</t>
+          <t>Randolph Joseph</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>21</v>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3112,48 +3110,26 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>SPM</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>29-jun</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>+18292032829</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Risairi Santana Rosario</t>
+          <t>Risaira Santana Rosario</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3162,7 +3138,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
@@ -3186,7 +3162,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -3195,27 +3171,27 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>28-mar</t>
+          <t>29-jun</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>+18293762582</t>
+          <t>+18292032829</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3227,16 +3203,16 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Roberto Figueroa</t>
+          <t>Risairi Santana Rosario</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
@@ -3260,7 +3236,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3269,25 +3245,27 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>2025</v>
+      </c>
       <c r="L38" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>12-may</t>
+          <t>28-mar</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>+18097171329</t>
+          <t>+18293762582</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3299,7 +3277,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Tommy Nova Nolasco</t>
+          <t>Roberto Figueroa</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3308,7 +3286,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
@@ -3332,36 +3310,34 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>2025</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>7-sep</t>
+          <t>12-may</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>+18492666296</t>
+          <t>+18097171329</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3373,16 +3349,16 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Wirna Miguelina Stapleton Pilier</t>
+          <t>Tommy Nova Nolasco</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
@@ -3406,34 +3382,36 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>2025</v>
+      </c>
       <c r="L40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>29-sep</t>
+          <t>7-sep</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>+82980199270</t>
+          <t>+18492666296</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -3445,69 +3423,67 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>José Ángel Tusen Russo</t>
+          <t>Wirna Miguelina Stapleton Pilier</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>29-sep</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>+82980199270</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
           <t>M</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>musica</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Coord. Música</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>2017</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>30-oct</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>+8493521430</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -3519,15 +3495,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Daylin</t>
+          <t>José Ángel Tusen Russo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3535,12 +3513,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Coord. Música</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -3550,26 +3528,48 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>30-oct</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>+8493521430</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Dorian Elina Rodriguez Belliard</t>
+          <t>Daylin</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3577,9 +3577,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>21</v>
-      </c>
+      <c r="C43" s="4" t="inlineStr"/>
       <c r="D43" s="9" t="inlineStr">
         <is>
           <t>musica</t>
@@ -3602,48 +3600,26 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Betania</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Punta Cana</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>2015</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>21-mar</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>+82998609950</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Ismarie Sthepanie Constanzo Ramos</t>
+          <t>Dorian Elina Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3652,7 +3628,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
@@ -3681,26 +3657,26 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>El Seibo / SPM</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>14-jun</t>
+          <t>21-mar</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>+18493865474</t>
+          <t>+82998609950</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
@@ -3717,16 +3693,16 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Leober Carrion Soriano</t>
+          <t>Ismarie Sthepanie Constanzo Ramos</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -3755,26 +3731,26 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>El Seibo / SPM</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>4-oct</t>
+          <t>14-jun</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>+18294401305</t>
+          <t>+18493865474</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -3791,16 +3767,16 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Mary Carmen Ramírez Vásquez</t>
+          <t>Leober Carrion Soriano</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
@@ -3833,22 +3809,22 @@
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>29-ago</t>
+          <t>4-oct</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>+18296937582</t>
+          <t>+18294401305</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -3865,57 +3841,81 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Frank Morales</t>
+          <t>Mary Carmen Ramírez Vásquez</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>musica</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Betania</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>29-ago</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>+18296937582</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>asesores</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Asesor + Banderín</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr"/>
-      <c r="N47" s="4" t="inlineStr"/>
-      <c r="O47" s="4" t="inlineStr"/>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Padre Paul Ramírez</t>
+          <t>Frank Morales</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3924,14 +3924,14 @@
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>asesores_espirituales</t>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>asesores</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Asesor Espiritual transversal</t>
+          <t>Asesor + Banderín</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Sor Angelina Lebrón</t>
+          <t>Padre Paul Ramírez</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Asesora Espiritual transversal</t>
+          <t>Asesor Espiritual transversal</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4013,50 +4013,50 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Johanny García</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sor Angelina Lebrón</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>asesores_cocina</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>Asesora Cocina</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>asesores_espirituales</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Asesora Espiritual transversal</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="12" t="inlineStr"/>
-      <c r="K50" s="12" t="inlineStr"/>
-      <c r="L50" s="12" t="inlineStr"/>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="12" t="inlineStr"/>
-      <c r="O50" s="12" t="inlineStr"/>
-      <c r="P50" s="12" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -4065,7 +4065,7 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Mary "Petra" Morales</t>
+          <t>Johanny García</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>Kamila Todd</t>
+          <t>Mary "Petra" Morales</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -4124,14 +4124,14 @@
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr"/>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>guias</t>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>asesores_cocina</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Backup Guía</t>
+          <t>Asesora Cocina</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>Leticia González</t>
+          <t>Kamila Todd</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
@@ -4174,14 +4174,14 @@
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr"/>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Asesora Comunidad La Vega</t>
+          <t>Backup Guía</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>Marleny</t>
+          <t>Leticia González</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Asesora Comunidad SD</t>
+          <t>Asesora Comunidad La Vega</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -4265,23 +4265,23 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>Rodolfo Telémaco</t>
+          <t>Marleny</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>guias</t>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Backup Guía</t>
+          <t>Asesora Comunidad SD</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4315,23 +4315,23 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>Sandrita</t>
+          <t>Rodolfo Telémaco</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr"/>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>asesores_diocesanos</t>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Asesora Comunidad SD</t>
+          <t>Backup Guía</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -4365,7 +4365,7 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>Scarlett Nivar</t>
+          <t>Sandrita</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
@@ -4374,14 +4374,14 @@
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>guias</t>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Backup Guía</t>
+          <t>Asesora Comunidad SD</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4415,23 +4415,23 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>Vacante Cocina (varón — candidato Randolph)</t>
+          <t>Scarlett Nivar</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>cocina</t>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>guias</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Backup Guía</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4592,20 +4592,38 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>Intersección (espiritual)</t>
+          <t>Intersección (diáspora)</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Equipo espiritual transversal: oración, intercesión, acompañamiento.</t>
+          <t>Vínculo con la diáspora — etecianos del 88 (y comunidad eteciana amplia) que residen fuera del país y apoyan al retiro: padrinazgo, oración, donaciones desde el exterior. Rol tradicional del equipo de Intersección.</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Asesores Espirituales (Padre Paul + Sor Angelina)</t>
+          <t>Por nombrar (Co-Dir decide)</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Finanzas / Tesorería (auxiliar)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Control de pagos, recibos, conciliación y reportes de gastos (planificado vs real). Auxilia a la Co-Dirección. Responde a la medida #3 del Informe Final ETC 85.</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Por nombrar dentro del equipo (Co-Dir decide)</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6671,7 +6689,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Versión de datos: v8-2026-06-02 · 47 operativos + 9 ampliados = 56 en el retiro.</t>
+          <t>Versión de datos: v8-2026-06-02 · 48 operativos + 8 ampliados = 56 en el retiro.</t>
         </is>
       </c>
     </row>

--- a/Equipo_ETC88.xlsx
+++ b/Equipo_ETC88.xlsx
@@ -2979,7 +2979,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Olanlly</t>
+          <t>Marian Olanlly Ortiz Carrasco</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2987,7 +2987,9 @@
           <t>F</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3019,10 +3021,14 @@
       <c r="L34" s="4" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr"/>
-      <c r="O34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3093,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>cocina</t>
@@ -3119,10 +3127,14 @@
       <c r="L36" s="4" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6135,115 +6147,55 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>Risaira Santana Rosario</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Aceptación</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>Una experiencia que alimente más mi fe y la de otros</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No dar lo mejor de mí, no poder tener la capacidad de dejar de lado las cosas que nos hacen humanos y nos impiden un encuentro pleno con cristo y no cumplir con las expectativas que me autoexijo a la hora de dar un sí </t>
-        </is>
-      </c>
+          <t>Marian Olanlly Ortiz Carrasco</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="20" t="inlineStr"/>
+      <c r="D34" s="20" t="inlineStr"/>
       <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ninguna </t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ninguna </t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ninguno </t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>Santa Rosario(madre). +1 809 474 2829</t>
-        </is>
-      </c>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr"/>
+      <c r="I34" s="20" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>Risairi Santana Rosario</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Desprendimiento</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Volver a vivir esa experiencia tan única y hermosa, dar de esta gracia que he recibido y servir.</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que soy muy tímida </t>
-        </is>
-      </c>
+          <t>Randolph Joseph</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="20" t="inlineStr"/>
       <c r="E35" s="20" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-      <c r="I35" s="20" t="inlineStr">
-        <is>
-          <t>Santa Rosario Reyes, mi madre, 809 475 2829</t>
-        </is>
-      </c>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+      <c r="I35" s="20" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>Roberto Figueroa</t>
+          <t>Risaira Santana Rosario</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Disposición</t>
+          <t>Aceptación</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renovar mi etc y por seguir formándome y compartir mi decesos de estar a los pies del Señor y poder mantenerme en su camino </t>
+          <t>Una experiencia que alimente más mi fe y la de otros</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unión familiar </t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reflejar el rostro de Jesús  desde el ejemplo </t>
-        </is>
-      </c>
+          <t xml:space="preserve">No dar lo mejor de mí, no poder tener la capacidad de dejar de lado las cosas que nos hacen humanos y nos impiden un encuentro pleno con cristo y no cumplir con las expectativas que me autoexijo a la hora de dar un sí </t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr"/>
       <c r="F36" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ninguna </t>
@@ -6251,137 +6203,227 @@
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t xml:space="preserve">Ninguna </t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>Nimguno</t>
+          <t xml:space="preserve">Ninguno </t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
-          <t>Josseline Aimee Cruz 809 714 1120</t>
+          <t>Santa Rosario(madre). +1 809 474 2829</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Tommy Nova Nolasco</t>
+          <t>Risairi Santana Rosario</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Entusiasmo</t>
+          <t>Desprendimiento</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vivir la experiencia detrás de cámaras </t>
+          <t>Volver a vivir esa experiencia tan única y hermosa, dar de esta gracia que he recibido y servir.</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Que soy muy tímida </t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>Mi consistencia en la fe</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="H37" s="20" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>Jaina Ramirez - Hermana - 829 964 0229</t>
+          <t>Santa Rosario Reyes, mi madre, 809 475 2829</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>Wirna Miguelina Stapleton Pilier</t>
+          <t>Roberto Figueroa</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Coherencia</t>
+          <t>Disposición</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un etc de servidores </t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr"/>
+          <t xml:space="preserve">Renovar mi etc y por seguir formándome y compartir mi decesos de estar a los pies del Señor y poder mantenerme en su camino </t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unión familiar </t>
+        </is>
+      </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">La vida en comunidad  </t>
+          <t xml:space="preserve">Reflejar el rostro de Jesús  desde el ejemplo </t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No </t>
+          <t xml:space="preserve">Ninguna </t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ninguna </t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ninguno </t>
+          <t>Nimguno</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>Juan M Stapleton papa 8097107944</t>
+          <t>Josseline Aimee Cruz 809 714 1120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
         <is>
+          <t>Tommy Nova Nolasco</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Entusiasmo</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vivir la experiencia detrás de cámaras </t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Mi consistencia en la fe</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>Jaina Ramirez - Hermana - 829 964 0229</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Wirna Miguelina Stapleton Pilier</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Coherencia</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un etc de servidores </t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr"/>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La vida en comunidad  </t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No </t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ninguna </t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ninguno </t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>Juan M Stapleton papa 8097107944</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
           <t>José Ángel Tusen Russo</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>Si el amor se acaba, se acaba el servicio.</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>La misma armonia y espontenedad de lo que somos.</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>Ningunos</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>La perseverancia.</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Alimentaria:
 Huevo
@@ -6391,207 +6433,207 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="20" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>Normalmente cargo con mis medicamentos</t>
         </is>
       </c>
-      <c r="I39" s="20" t="inlineStr">
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>Dorian,  829- 986-0985</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Dorian Elina Rodriguez Belliard</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>Espero vivir y recordar el amor de cada uno de mis amigos de comunidad y el gran sacrificio detrás de cada pequeño detalle del retiro.</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>Ser más misericordiosa, ver a los demás con los ojos de Dios</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>Polvo, gatos, etc.. (pero no se preocupen tengo siempre tengo antialérgico)</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>Migraña</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>Antialérgicos, antimigrañosos</t>
         </is>
       </c>
-      <c r="I40" s="20" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">8493521430 Jose Tusen </t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Ismarie Sthepanie Constanzo Ramos</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Amor.</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Dejarme usar genuinamente por Dios para poder servir enteramente, revivir mi retiro y dar lo que deba de mí para que así como yo viví el mío, otros puedan hacerlo a través de mí y del equipo. 
 Integrarme también con el equipo/hermanos de comunidad. </t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ansiedad al futuro, a no ser suficiente o no escuchar la voz de Dios que me llama y por ende no cumplir con lo que Él ha soñado para mi, tanto espiritualmente como en mi área profesional. </t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Si, la confianza y la falta de voluntad/pereza. </t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Neo-Melubrina (metamizol sódico) </t>
         </is>
       </c>
-      <c r="G41" s="20" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ninguna. </t>
         </is>
       </c>
-      <c r="H41" s="20" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Analgésicos y triptanes. </t>
         </is>
       </c>
-      <c r="I41" s="20" t="inlineStr">
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Digna Ramos (madre) 829-705-2966
 Enrique Constanzo (Padre) 809-815-6852 </t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Leober Carrion Soriano</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Oportunidad</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Seguir viendo a Dios en cada uno del equipo y participantes </t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>Un poco a liderar o contacto directo con los participantes (por ejemplo: Guia)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Si, volver a conectar conmigo como algunas vez lo fue. </t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>Ninguno</t>
         </is>
       </c>
-      <c r="I42" s="20" t="inlineStr">
+      <c r="I44" s="20" t="inlineStr">
         <is>
           <t>Aneurys Soriano- Madre- 8294301304</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Mary Carmen Ramírez Vásquez</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Poder dar un poco de lo que tengo a los demás </t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Miedo escénico y a salir de mi zona de comfort </t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Creo que no </t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ninguna </t>
         </is>
       </c>
-      <c r="G43" s="20" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Postquirurgica de la una corrección de escoliosis </t>
         </is>
       </c>
-      <c r="H43" s="20" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="I43" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>Carmen Vasquez (madre) 829-313-3130, Haniel González (novio) 809-929-2042</t>
         </is>
